--- a/docs/harness/wirelist/EngineRoom-C-wirelist.xlsx
+++ b/docs/harness/wirelist/EngineRoom-C-wirelist.xlsx
@@ -1702,10 +1702,14 @@
       <c r="AB7" s="37" t="inlineStr"/>
       <c r="AC7" s="38" t="inlineStr"/>
       <c r="AD7" s="38" t="inlineStr"/>
-      <c r="AE7" s="38" t="inlineStr"/>
+      <c r="AE7" s="38" t="inlineStr">
+        <is>
+          <t>end t_gnd_ea_2: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF7" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_gnd_ea_2 (Ground stud EA, RH front fender (EWD ground point EA)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG7" s="38" t="inlineStr"/>
@@ -2881,10 +2885,14 @@
       <c r="AB16" s="53" t="inlineStr"/>
       <c r="AC16" s="54" t="inlineStr"/>
       <c r="AD16" s="54" t="inlineStr"/>
-      <c r="AE16" s="54" t="inlineStr"/>
+      <c r="AE16" s="54" t="inlineStr">
+        <is>
+          <t>end t_gnd_ea_h3: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF16" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_gnd_ea_h3 (Ground stud EA, RH front fender (EWD ground point EA)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG16" s="54" t="inlineStr"/>
@@ -2984,10 +2992,14 @@
       <c r="AB17" s="37" t="inlineStr"/>
       <c r="AC17" s="38" t="inlineStr"/>
       <c r="AD17" s="38" t="inlineStr"/>
-      <c r="AE17" s="38" t="inlineStr"/>
+      <c r="AE17" s="38" t="inlineStr">
+        <is>
+          <t>end t_gnd_ea_h4: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF17" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_gnd_ea_h4 (Ground stud EA, RH front fender (EWD ground point EA)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG17" s="38" t="inlineStr"/>
@@ -3877,12 +3889,12 @@
       <c r="AD24" s="54" t="inlineStr"/>
       <c r="AE24" s="54" t="inlineStr">
         <is>
-          <t>channels.csv mrs_eps a2 Ground (CHASSIS_ENG)</t>
+          <t>channels.csv mrs_eps a2 Ground (CHASSIS_ENG); end t_eng_block_3: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF24" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_eng_block_3 (Engine block ground stud, lug 3 (Route 1 point 5)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG24" s="54" t="inlineStr"/>
@@ -3986,12 +3998,12 @@
       <c r="AD25" s="38" t="inlineStr"/>
       <c r="AE25" s="38" t="inlineStr">
         <is>
-          <t>fuse-box plan pdb GND (53.5 AWG)</t>
+          <t>fuse-box plan pdb GND (53.5 AWG); end t_gnd_id: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF25" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_gnd_id (Ground stud ID, left kick panel (EWD ground point ID)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG25" s="38" t="inlineStr"/>
@@ -4095,12 +4107,12 @@
       <c r="AD26" s="54" t="inlineStr"/>
       <c r="AE26" s="54" t="inlineStr">
         <is>
-          <t>fuse-box plan pdb GND (53.5 AWG)</t>
+          <t>fuse-box plan pdb GND (53.5 AWG); end t_gnd_ig: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF26" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_gnd_ig (Ground bolt IG, right kick (EWD ground point IG)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG26" s="54" t="inlineStr"/>
@@ -4204,10 +4216,14 @@
       <c r="AB27" s="37" t="inlineStr"/>
       <c r="AC27" s="38" t="inlineStr"/>
       <c r="AD27" s="38" t="inlineStr"/>
-      <c r="AE27" s="38" t="inlineStr"/>
+      <c r="AE27" s="38" t="inlineStr">
+        <is>
+          <t>end t_gnd_ea: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF27" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_gnd_ea (Ground stud EA, RH front fender (EWD ground point EA)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG27" s="38" t="inlineStr"/>
@@ -4331,12 +4347,12 @@
       </c>
       <c r="AE28" s="54" t="inlineStr">
         <is>
-          <t>flying lead FL_F7_C2: EWD F7 pin 2 W-B (factory wiring; new wire here)</t>
+          <t>flying lead FL_F7_C2: EWD F7 pin 2 W-B (factory wiring; new wire here); end t_gnd_eb_f7: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF28" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_gnd_eb_f7 (Ground stud EB, LH front fender (EWD ground point EB)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG28" s="54" t="inlineStr"/>
@@ -4460,12 +4476,12 @@
       </c>
       <c r="AE29" s="38" t="inlineStr">
         <is>
-          <t>flying lead FL_F8_C2: EWD F8 pin 2 W-B (factory wiring; new wire here)</t>
+          <t>flying lead FL_F8_C2: EWD F8 pin 2 W-B (factory wiring; new wire here); end t_gnd_ea_f8: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF29" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_gnd_ea_f8 (Ground stud EA, RH front fender (EWD ground point EA)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG29" s="38" t="inlineStr"/>
@@ -4722,7 +4738,7 @@
       </c>
       <c r="AE31" s="38" t="inlineStr">
         <is>
-          <t>flying lead FL_H1_C1: EWD H1 pin 1 R-L (factory wiring; new wire here); splice sp_hl_high named in SoT</t>
+          <t>flying lead FL_H1_C1: EWD H1 pin 1 R-L (factory wiring; new wire here); splice sp_hl_high: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF31" s="38" t="inlineStr">
@@ -4853,7 +4869,7 @@
       </c>
       <c r="AE32" s="54" t="inlineStr">
         <is>
-          <t>flying lead FL_H1_C2: EWD H1 pin 2 R-W (factory wiring; new wire here); splice sp_hl_low named in SoT</t>
+          <t>flying lead FL_H1_C2: EWD H1 pin 2 R-W (factory wiring; new wire here); splice sp_hl_low: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF32" s="54" t="inlineStr">
@@ -4984,7 +5000,7 @@
       </c>
       <c r="AE33" s="38" t="inlineStr">
         <is>
-          <t>flying lead FL_H2_C1: EWD H2 pin 1 R-L (factory wiring; new wire here); splice sp_hl_high named in SoT</t>
+          <t>flying lead FL_H2_C1: EWD H2 pin 1 R-L (factory wiring; new wire here); splice sp_hl_high: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF33" s="38" t="inlineStr">
@@ -5115,7 +5131,7 @@
       </c>
       <c r="AE34" s="54" t="inlineStr">
         <is>
-          <t>flying lead FL_H2_C2: EWD H2 pin 2 R-W (factory wiring; new wire here); splice sp_hl_low named in SoT</t>
+          <t>flying lead FL_H2_C2: EWD H2 pin 2 R-W (factory wiring; new wire here); splice sp_hl_low: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF34" s="54" t="inlineStr">
@@ -5246,7 +5262,7 @@
       </c>
       <c r="AE35" s="38" t="inlineStr">
         <is>
-          <t>flying lead FL_OEM_IE1_C7: EWD IE1 pin 7 G-Y; splice sp_rtr_r3_4 named in SoT</t>
+          <t>flying lead FL_OEM_IE1_C7: EWD IE1 pin 7 G-Y; splice sp_rtr_r3_4: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF35" s="38" t="inlineStr">
@@ -5508,7 +5524,7 @@
       </c>
       <c r="AE37" s="38" t="inlineStr">
         <is>
-          <t>flying lead FL_OEM_IE1_C9: EWD IE1 pin 9 G-Y; splice sp_rtr_close named in SoT</t>
+          <t>flying lead FL_OEM_IE1_C9: EWD IE1 pin 9 G-Y; splice sp_rtr_close: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF37" s="38" t="inlineStr">
@@ -5766,7 +5782,7 @@
       </c>
       <c r="AE39" s="38" t="inlineStr">
         <is>
-          <t>flying lead FL_OEM_IE1_C14: EWD IE1 pin 14 G; splice sp_rtr_r2_4 named in SoT</t>
+          <t>flying lead FL_OEM_IE1_C14: EWD IE1 pin 14 G; splice sp_rtr_r2_4: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF39" s="38" t="inlineStr">
@@ -6028,7 +6044,7 @@
       </c>
       <c r="AE41" s="38" t="inlineStr">
         <is>
-          <t>flying lead FL_OEM_IE1_C16: EWD IE1 pin 16 G-W; splice sp_rtr_open named in SoT</t>
+          <t>flying lead FL_OEM_IE1_C16: EWD IE1 pin 16 G-W; splice sp_rtr_open: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF41" s="38" t="inlineStr">
@@ -6550,7 +6566,7 @@
       </c>
       <c r="AE45" s="38" t="inlineStr">
         <is>
-          <t>flying lead FL_OEM_JB1_1H_C6: EWD J/B1 pin 1H-6 G; splice sp_clr named in SoT</t>
+          <t>flying lead FL_OEM_JB1_1H_C6: EWD J/B1 pin 1H-6 G; splice sp_clr: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF45" s="38" t="inlineStr">
@@ -6814,7 +6830,7 @@
       </c>
       <c r="AE47" s="38" t="inlineStr">
         <is>
-          <t>flying lead FL_R2_C5: EWD R2 pin 5 W-B (factory wiring; new wire here); splice sp_rtr_gnd_r2 named in SoT</t>
+          <t>flying lead FL_R2_C5: EWD R2 pin 5 W-B (factory wiring; new wire here); splice sp_rtr_gnd_r2: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF47" s="38" t="inlineStr">
@@ -6945,7 +6961,7 @@
       </c>
       <c r="AE48" s="54" t="inlineStr">
         <is>
-          <t>flying lead FL_R3_C5: EWD R3 pin 5 W-B (factory wiring; new wire here); splice sp_rtr_gnd_r3 named in SoT</t>
+          <t>flying lead FL_R3_C5: EWD R3 pin 5 W-B (factory wiring; new wire here); splice sp_rtr_gnd_r3: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF48" s="54" t="inlineStr">
@@ -7334,7 +7350,7 @@
       </c>
       <c r="AE51" s="38" t="inlineStr">
         <is>
-          <t>splice sp_clr named in SoT; flying lead FL_F7_C1: EWD F7 pin 1 G (factory wiring; new wire here)</t>
+          <t>splice sp_clr: node of the wire list (SoT); flying lead FL_F7_C1: EWD F7 pin 1 G (factory wiring; new wire here)</t>
         </is>
       </c>
       <c r="AF51" s="38" t="inlineStr">
@@ -7461,7 +7477,7 @@
       </c>
       <c r="AE52" s="54" t="inlineStr">
         <is>
-          <t>splice sp_clr named in SoT; flying lead FL_F8_C1: EWD F8 pin 1 G (factory wiring; new wire here)</t>
+          <t>splice sp_clr: node of the wire list (SoT); flying lead FL_F8_C1: EWD F8 pin 1 G (factory wiring; new wire here)</t>
         </is>
       </c>
       <c r="AF52" s="54" t="inlineStr">
@@ -7592,7 +7608,7 @@
       </c>
       <c r="AE53" s="38" t="inlineStr">
         <is>
-          <t>splice sp_hl_high named in SoT; flying lead FL_OEM_IE1_C11: EWD IE1 pin 11 R-L</t>
+          <t>splice sp_hl_high: node of the wire list (SoT); flying lead FL_OEM_IE1_C11: EWD IE1 pin 11 R-L</t>
         </is>
       </c>
       <c r="AF53" s="38" t="inlineStr">
@@ -7723,7 +7739,7 @@
       </c>
       <c r="AE54" s="54" t="inlineStr">
         <is>
-          <t>splice sp_hl_low named in SoT; flying lead FL_OEM_IE1_C18: EWD IE1 pin 18 R-W</t>
+          <t>splice sp_hl_low: node of the wire list (SoT); flying lead FL_OEM_IE1_C18: EWD IE1 pin 18 R-W</t>
         </is>
       </c>
       <c r="AF54" s="54" t="inlineStr">
@@ -7832,10 +7848,14 @@
       <c r="AB55" s="37" t="inlineStr"/>
       <c r="AC55" s="38" t="inlineStr"/>
       <c r="AD55" s="38" t="inlineStr"/>
-      <c r="AE55" s="38" t="inlineStr"/>
+      <c r="AE55" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_horn: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF55" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_horn is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG55" s="38" t="inlineStr"/>
@@ -7939,10 +7959,14 @@
       <c r="AB56" s="53" t="inlineStr"/>
       <c r="AC56" s="54" t="inlineStr"/>
       <c r="AD56" s="54" t="inlineStr"/>
-      <c r="AE56" s="54" t="inlineStr"/>
+      <c r="AE56" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_horn: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF56" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_horn is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG56" s="54" t="inlineStr"/>
@@ -8068,7 +8092,7 @@
       </c>
       <c r="AE57" s="38" t="inlineStr">
         <is>
-          <t>splice sp_rtr_close named in SoT; flying lead FL_R2_C3: EWD R2 pin 3 G-Y (factory wiring; new wire here)</t>
+          <t>splice sp_rtr_close: node of the wire list (SoT); flying lead FL_R2_C3: EWD R2 pin 3 G-Y (factory wiring; new wire here)</t>
         </is>
       </c>
       <c r="AF57" s="38" t="inlineStr">
@@ -8199,7 +8223,7 @@
       </c>
       <c r="AE58" s="54" t="inlineStr">
         <is>
-          <t>splice sp_rtr_close named in SoT; flying lead FL_R3_C3: EWD R3 pin 3 G-Y (factory wiring; new wire here)</t>
+          <t>splice sp_rtr_close: node of the wire list (SoT); flying lead FL_R3_C3: EWD R3 pin 3 G-Y (factory wiring; new wire here)</t>
         </is>
       </c>
       <c r="AF58" s="54" t="inlineStr">
@@ -8312,12 +8336,12 @@
       <c r="AD59" s="38" t="inlineStr"/>
       <c r="AE59" s="38" t="inlineStr">
         <is>
-          <t>splice sp_rtr_gnd_r2 named in SoT</t>
+          <t>splice sp_rtr_gnd_r2: node of the wire list (SoT); end t_gnd_eb_rtr: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF59" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_gnd_eb_rtr (Ground stud EB, LH front fender (EWD ground point EB)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG59" s="38" t="inlineStr"/>
@@ -8425,12 +8449,12 @@
       <c r="AD60" s="54" t="inlineStr"/>
       <c r="AE60" s="54" t="inlineStr">
         <is>
-          <t>splice sp_rtr_gnd_r3 named in SoT</t>
+          <t>splice sp_rtr_gnd_r3: node of the wire list (SoT); end t_gnd_eb_rtr: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF60" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_gnd_eb_rtr (Ground stud EB, LH front fender (EWD ground point EB)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG60" s="54" t="inlineStr"/>
@@ -8556,7 +8580,7 @@
       </c>
       <c r="AE61" s="38" t="inlineStr">
         <is>
-          <t>splice sp_rtr_open named in SoT; flying lead FL_R2_C1: EWD R2 pin 1 G-W (factory wiring; new wire here)</t>
+          <t>splice sp_rtr_open: node of the wire list (SoT); flying lead FL_R2_C1: EWD R2 pin 1 G-W (factory wiring; new wire here)</t>
         </is>
       </c>
       <c r="AF61" s="38" t="inlineStr">
@@ -8687,7 +8711,7 @@
       </c>
       <c r="AE62" s="54" t="inlineStr">
         <is>
-          <t>splice sp_rtr_open named in SoT; flying lead FL_R3_C1: EWD R3 pin 1 G-W (factory wiring; new wire here)</t>
+          <t>splice sp_rtr_open: node of the wire list (SoT); flying lead FL_R3_C1: EWD R3 pin 1 G-W (factory wiring; new wire here)</t>
         </is>
       </c>
       <c r="AF62" s="54" t="inlineStr">
@@ -8814,7 +8838,7 @@
       </c>
       <c r="AE63" s="38" t="inlineStr">
         <is>
-          <t>splice sp_rtr_r2_4 named in SoT; flying lead FL_R2_C4: EWD R2 pin 4 G (factory wiring; new wire here)</t>
+          <t>splice sp_rtr_r2_4: node of the wire list (SoT); flying lead FL_R2_C4: EWD R2 pin 4 G (factory wiring; new wire here)</t>
         </is>
       </c>
       <c r="AF63" s="38" t="inlineStr">
@@ -8945,7 +8969,7 @@
       </c>
       <c r="AE64" s="54" t="inlineStr">
         <is>
-          <t>splice sp_rtr_r3_4 named in SoT; flying lead FL_R3_C4: EWD R3 pin 4 G-Y (factory wiring; new wire here)</t>
+          <t>splice sp_rtr_r3_4: node of the wire list (SoT); flying lead FL_R3_C4: EWD R3 pin 4 G-Y (factory wiring; new wire here)</t>
         </is>
       </c>
       <c r="AF64" s="54" t="inlineStr">
@@ -9046,10 +9070,14 @@
       <c r="AB65" s="37" t="inlineStr"/>
       <c r="AC65" s="38" t="inlineStr"/>
       <c r="AD65" s="38" t="inlineStr"/>
-      <c r="AE65" s="38" t="inlineStr"/>
+      <c r="AE65" s="38" t="inlineStr">
+        <is>
+          <t>end t_eng_block_2: end row of the wire list (SoT); end t_gnd_eb: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF65" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_eng_block_2 (Engine block ground stud, lug 2 (Route 1 point 5)) is drawing-only: not named in the SoT; end t_gnd_eb (Ground stud EB, LH front fender (EWD ground point EB)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG65" s="38" t="inlineStr"/>
@@ -9615,7 +9643,7 @@
       </c>
       <c r="L3" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -9671,7 +9699,7 @@
       </c>
       <c r="L4" s="54" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -9727,7 +9755,7 @@
       </c>
       <c r="L5" s="38" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9811,7 @@
       </c>
       <c r="L6" s="54" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -9839,7 +9867,7 @@
       </c>
       <c r="L7" s="38" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -9895,7 +9923,7 @@
       </c>
       <c r="L8" s="54" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9979,7 @@
       </c>
       <c r="L9" s="38" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -10007,7 +10035,7 @@
       </c>
       <c r="L10" s="54" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -10063,7 +10091,7 @@
       </c>
       <c r="L11" s="38" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -10119,7 +10147,7 @@
       </c>
       <c r="L12" s="54" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelist/EngineRoom-C-wirelist.xlsx
+++ b/docs/harness/wirelist/EngineRoom-C-wirelist.xlsx
@@ -1792,7 +1792,7 @@
       </c>
       <c r="R8" s="47" t="inlineStr">
         <is>
-          <t>+12V DM 20A (LOGIC BUS1-5)</t>
+          <t>+12V DOME feed to J/B1 (LOGIC BUS1-5)</t>
         </is>
       </c>
       <c r="S8" s="48" t="inlineStr"/>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="R9" s="31" t="inlineStr">
         <is>
-          <t>+12V WL 15A (LOGIC BUS1-6)</t>
+          <t>+12V Door lock feed (LOGIC BUS1-6)</t>
         </is>
       </c>
       <c r="S9" s="32" t="inlineStr"/>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="R10" s="47" t="inlineStr">
         <is>
-          <t>+12V ALTS 2A (LOGIC BUS1-9)</t>
+          <t>+12V Alt S battery sense (LOGIC BUS1-9)</t>
         </is>
       </c>
       <c r="S10" s="48" t="inlineStr"/>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="R11" s="31" t="inlineStr">
         <is>
-          <t>+12V ACPS 10A (POWER ACPS)</t>
+          <t>+12V A/C press sw feed (POWER ACPS)</t>
         </is>
       </c>
       <c r="S11" s="32" t="inlineStr"/>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="R12" s="47" t="inlineStr">
         <is>
-          <t>+12V RTR 30A (POWER AMI OUT-2)</t>
+          <t>+12V Retract relay feed (POWER AMI OUT-2)</t>
         </is>
       </c>
       <c r="S12" s="48" t="inlineStr"/>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="R13" s="31" t="inlineStr">
         <is>
-          <t>+12V AM1 40A (POWER AMI OUT-3)</t>
+          <t>+12V AM1 feed to IE1 (POWER AMI OUT-3)</t>
         </is>
       </c>
       <c r="S13" s="32" t="inlineStr"/>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="R14" s="47" t="inlineStr">
         <is>
-          <t>+12V AM2 30A (POWER AMI OUT-4)</t>
+          <t>+12V AM2 feed to IE1 (POWER AMI OUT-4)</t>
         </is>
       </c>
       <c r="S14" s="48" t="inlineStr"/>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="R15" s="31" t="inlineStr">
         <is>
-          <t>+12V JB1 60A (POWER AMI OUT-5)</t>
+          <t>+12V J/B1 main feed (POWER AMI OUT-5)</t>
         </is>
       </c>
       <c r="S15" s="32" t="inlineStr"/>
@@ -2865,7 +2865,9 @@
       </c>
       <c r="S16" s="48" t="inlineStr"/>
       <c r="T16" s="48" t="inlineStr"/>
-      <c r="U16" s="49" t="inlineStr"/>
+      <c r="U16" s="49" t="n">
+        <v>16</v>
+      </c>
       <c r="V16" s="50" t="inlineStr">
         <is>
           <t>Black</t>
@@ -2972,7 +2974,9 @@
       </c>
       <c r="S17" s="32" t="inlineStr"/>
       <c r="T17" s="32" t="inlineStr"/>
-      <c r="U17" s="33" t="inlineStr"/>
+      <c r="U17" s="33" t="n">
+        <v>16</v>
+      </c>
       <c r="V17" s="34" t="inlineStr">
         <is>
           <t>Black</t>

--- a/docs/harness/wirelist/EngineRoom-C-wirelist.xlsx
+++ b/docs/harness/wirelist/EngineRoom-C-wirelist.xlsx
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="H4" s="41" t="n">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="I4" s="42" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
       <c r="AD4" s="54" t="inlineStr"/>
       <c r="AE4" s="54" t="inlineStr">
         <is>
-          <t>DRB102 42 = section A c35 'MRS EPS pump logic enable (fuse box LOGIC MRS, 7.5'; channels.csv mrs_eps c1 Enable (MRS_EN)</t>
+          <t>DRB102 83 = loom A c83 'EHPS enable +12 V'; channels.csv mrs_eps c1 Enable (MRS_EN)</t>
         </is>
       </c>
       <c r="AF4" s="54" t="inlineStr">
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="H5" s="25" t="n">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="I5" s="26" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
       <c r="AD5" s="38" t="inlineStr"/>
       <c r="AE5" s="38" t="inlineStr">
         <is>
-          <t>DRB102 44 = section A c36 'Aux 7 MRS speed-out (ECU A27)'; channels.csv mrs_eps b2 SPD (AUX7_MRS_SPD)</t>
+          <t>DRB102 84 = loom A c84 'ECU-A A27'; channels.csv mrs_eps b2 SPD (AUX7_MRS_SPD)</t>
         </is>
       </c>
       <c r="AF5" s="38" t="inlineStr">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="H6" s="41" t="n">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
@@ -1555,12 +1555,12 @@
       <c r="P6" s="45" t="inlineStr"/>
       <c r="Q6" s="46" t="inlineStr">
         <is>
-          <t>DRB102.56</t>
+          <t>DRB102.85</t>
         </is>
       </c>
       <c r="R6" s="47" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-) (DRB102 56)</t>
+          <t>EHPS relay coil (-) (DRB102 85)</t>
         </is>
       </c>
       <c r="S6" s="48" t="inlineStr"/>
@@ -1589,7 +1589,7 @@
       <c r="AD6" s="54" t="inlineStr"/>
       <c r="AE6" s="54" t="inlineStr">
         <is>
-          <t>DRB102 56 = section A c27 'EPS relay coil 85 (R22) - from the MR-S pump B5'; channels.csv mrs_eps b5 Relay (MRS_RLY)</t>
+          <t>DRB102 85 = loom A c85 'EHPS relay coil (-)'; channels.csv mrs_eps b5 Relay (MRS_RLY)</t>
         </is>
       </c>
       <c r="AF6" s="54" t="inlineStr">

--- a/docs/harness/wirelist/EngineRoom-C-wirelist.xlsx
+++ b/docs/harness/wirelist/EngineRoom-C-wirelist.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="V3" s="34" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W3" s="34" t="inlineStr"/>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="V5" s="34" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W5" s="34" t="inlineStr"/>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="V6" s="50" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W6" s="50" t="inlineStr"/>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="V11" s="34" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W11" s="34" t="inlineStr"/>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="V13" s="34" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W13" s="34" t="inlineStr"/>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="V14" s="50" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W14" s="50" t="inlineStr"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="V15" s="34" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W15" s="34" t="inlineStr"/>
@@ -4312,14 +4312,10 @@
       </c>
       <c r="V28" s="50" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="W28" s="50" t="inlineStr">
-        <is>
           <t>Black</t>
         </is>
       </c>
+      <c r="W28" s="50" t="inlineStr"/>
       <c r="X28" s="50" t="inlineStr">
         <is>
           <t>White</t>
@@ -4441,14 +4437,10 @@
       </c>
       <c r="V29" s="34" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="W29" s="34" t="inlineStr">
-        <is>
           <t>Black</t>
         </is>
       </c>
+      <c r="W29" s="34" t="inlineStr"/>
       <c r="X29" s="34" t="inlineStr">
         <is>
           <t>White</t>
@@ -4572,14 +4564,10 @@
       </c>
       <c r="V30" s="50" t="inlineStr">
         <is>
-          <t>Blue</t>
-        </is>
-      </c>
-      <c r="W30" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="W30" s="50" t="inlineStr"/>
       <c r="X30" s="50" t="inlineStr">
         <is>
           <t>Blue-Yellow</t>
@@ -4708,11 +4696,7 @@
           <t>Red</t>
         </is>
       </c>
-      <c r="W31" s="34" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W31" s="34" t="inlineStr"/>
       <c r="X31" s="34" t="inlineStr">
         <is>
           <t>White-Yellow</t>
@@ -4839,11 +4823,7 @@
           <t>Red</t>
         </is>
       </c>
-      <c r="W32" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+      <c r="W32" s="50" t="inlineStr"/>
       <c r="X32" s="50" t="inlineStr">
         <is>
           <t>White-White</t>
@@ -4970,11 +4950,7 @@
           <t>Red</t>
         </is>
       </c>
-      <c r="W33" s="34" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W33" s="34" t="inlineStr"/>
       <c r="X33" s="34" t="inlineStr">
         <is>
           <t>White-Yellow</t>
@@ -5101,11 +5077,7 @@
           <t>Red</t>
         </is>
       </c>
-      <c r="W34" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+      <c r="W34" s="50" t="inlineStr"/>
       <c r="X34" s="50" t="inlineStr">
         <is>
           <t>White-White</t>
@@ -5229,14 +5201,10 @@
       </c>
       <c r="V35" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="W35" s="34" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="W35" s="34" t="inlineStr"/>
       <c r="X35" s="34" t="inlineStr">
         <is>
           <t>Blue</t>
@@ -5358,14 +5326,10 @@
       </c>
       <c r="V36" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="W36" s="50" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="W36" s="50" t="inlineStr"/>
       <c r="X36" s="50" t="inlineStr">
         <is>
           <t>Blue</t>
@@ -5491,14 +5455,10 @@
       </c>
       <c r="V37" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="W37" s="34" t="inlineStr">
-        <is>
           <t>Yellow</t>
         </is>
       </c>
+      <c r="W37" s="34" t="inlineStr"/>
       <c r="X37" s="34" t="inlineStr">
         <is>
           <t>Blue</t>
@@ -5620,14 +5580,10 @@
       </c>
       <c r="V38" s="50" t="inlineStr">
         <is>
-          <t>Blue</t>
-        </is>
-      </c>
-      <c r="W38" s="50" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="W38" s="50" t="inlineStr"/>
       <c r="X38" s="50" t="inlineStr">
         <is>
           <t>Blue-Yellow</t>
@@ -5753,7 +5709,7 @@
       </c>
       <c r="V39" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W39" s="34" t="inlineStr"/>
@@ -5878,14 +5834,10 @@
       </c>
       <c r="V40" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="W40" s="50" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="W40" s="50" t="inlineStr"/>
       <c r="X40" s="50" t="inlineStr">
         <is>
           <t>Blue</t>
@@ -6011,14 +5963,10 @@
       </c>
       <c r="V41" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="W41" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="W41" s="34" t="inlineStr"/>
       <c r="X41" s="34" t="inlineStr">
         <is>
           <t>Blue</t>
@@ -6140,14 +6088,10 @@
       </c>
       <c r="V42" s="50" t="inlineStr">
         <is>
-          <t>Blue</t>
-        </is>
-      </c>
-      <c r="W42" s="50" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="W42" s="50" t="inlineStr"/>
       <c r="X42" s="50" t="inlineStr">
         <is>
           <t>Blue-Yellow</t>
@@ -6273,14 +6217,10 @@
       </c>
       <c r="V43" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="W43" s="34" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="W43" s="34" t="inlineStr"/>
       <c r="X43" s="34" t="inlineStr">
         <is>
           <t>Blue-Yellow-Yellow</t>
@@ -6406,7 +6346,7 @@
       </c>
       <c r="V44" s="50" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W44" s="50" t="inlineStr"/>
@@ -6537,7 +6477,7 @@
       </c>
       <c r="V45" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W45" s="34" t="inlineStr"/>
@@ -6664,14 +6604,10 @@
       </c>
       <c r="V46" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="W46" s="50" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="W46" s="50" t="inlineStr"/>
       <c r="X46" s="50" t="inlineStr">
         <is>
           <t>Blue-Yellow-Yellow</t>
@@ -6797,14 +6733,10 @@
       </c>
       <c r="V47" s="34" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="W47" s="34" t="inlineStr">
-        <is>
           <t>Black</t>
         </is>
       </c>
+      <c r="W47" s="34" t="inlineStr"/>
       <c r="X47" s="34" t="inlineStr">
         <is>
           <t>Blue</t>
@@ -6928,14 +6860,10 @@
       </c>
       <c r="V48" s="50" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="W48" s="50" t="inlineStr">
-        <is>
           <t>Black</t>
         </is>
       </c>
+      <c r="W48" s="50" t="inlineStr"/>
       <c r="X48" s="50" t="inlineStr">
         <is>
           <t>Blue</t>
@@ -7059,14 +6987,10 @@
       </c>
       <c r="V49" s="34" t="inlineStr">
         <is>
-          <t>Blue</t>
-        </is>
-      </c>
-      <c r="W49" s="34" t="inlineStr">
-        <is>
           <t>Red</t>
         </is>
       </c>
+      <c r="W49" s="34" t="inlineStr"/>
       <c r="X49" s="34" t="inlineStr">
         <is>
           <t>Blue-White-Blue</t>
@@ -7192,7 +7116,7 @@
       </c>
       <c r="V50" s="50" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W50" s="50" t="inlineStr"/>
@@ -7321,7 +7245,7 @@
       </c>
       <c r="V51" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W51" s="34" t="inlineStr"/>
@@ -7448,7 +7372,7 @@
       </c>
       <c r="V52" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W52" s="50" t="inlineStr"/>
@@ -7578,11 +7502,7 @@
           <t>Red</t>
         </is>
       </c>
-      <c r="W53" s="34" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W53" s="34" t="inlineStr"/>
       <c r="X53" s="34" t="inlineStr">
         <is>
           <t>White-Yellow</t>
@@ -7709,11 +7629,7 @@
           <t>Red</t>
         </is>
       </c>
-      <c r="W54" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+      <c r="W54" s="50" t="inlineStr"/>
       <c r="X54" s="50" t="inlineStr">
         <is>
           <t>White-White</t>
@@ -8059,14 +7975,10 @@
       </c>
       <c r="V57" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="W57" s="34" t="inlineStr">
-        <is>
           <t>Yellow</t>
         </is>
       </c>
+      <c r="W57" s="34" t="inlineStr"/>
       <c r="X57" s="34" t="inlineStr">
         <is>
           <t>Blue</t>
@@ -8190,14 +8102,10 @@
       </c>
       <c r="V58" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="W58" s="50" t="inlineStr">
-        <is>
           <t>Yellow</t>
         </is>
       </c>
+      <c r="W58" s="50" t="inlineStr"/>
       <c r="X58" s="50" t="inlineStr">
         <is>
           <t>Blue</t>
@@ -8319,14 +8227,10 @@
       </c>
       <c r="V59" s="34" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="W59" s="34" t="inlineStr">
-        <is>
           <t>Black</t>
         </is>
       </c>
+      <c r="W59" s="34" t="inlineStr"/>
       <c r="X59" s="34" t="inlineStr">
         <is>
           <t>Blue</t>
@@ -8432,14 +8336,10 @@
       </c>
       <c r="V60" s="50" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="W60" s="50" t="inlineStr">
-        <is>
           <t>Black</t>
         </is>
       </c>
+      <c r="W60" s="50" t="inlineStr"/>
       <c r="X60" s="50" t="inlineStr">
         <is>
           <t>Blue</t>
@@ -8547,14 +8447,10 @@
       </c>
       <c r="V61" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="W61" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="W61" s="34" t="inlineStr"/>
       <c r="X61" s="34" t="inlineStr">
         <is>
           <t>Blue</t>
@@ -8678,14 +8574,10 @@
       </c>
       <c r="V62" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="W62" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="W62" s="50" t="inlineStr"/>
       <c r="X62" s="50" t="inlineStr">
         <is>
           <t>Blue</t>
@@ -8809,7 +8701,7 @@
       </c>
       <c r="V63" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W63" s="34" t="inlineStr"/>
@@ -8936,14 +8828,10 @@
       </c>
       <c r="V64" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="W64" s="50" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="W64" s="50" t="inlineStr"/>
       <c r="X64" s="50" t="inlineStr">
         <is>
           <t>Blue</t>

--- a/docs/harness/wirelist/EngineRoom-C-wirelist.xlsx
+++ b/docs/harness/wirelist/EngineRoom-C-wirelist.xlsx
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D4" s="39" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="E4" s="40" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="F4" s="41" t="inlineStr">
         <is>
-          <t>bh_a_eng</t>
+          <t>bh_eng</t>
         </is>
       </c>
       <c r="G4" s="42" t="inlineStr">
@@ -1347,7 +1347,7 @@
       <c r="AD4" s="54" t="inlineStr"/>
       <c r="AE4" s="54" t="inlineStr">
         <is>
-          <t>DRB102 83 = loom A c83 'EHPS enable +12 V'; channels.csv mrs_eps c1 Enable (MRS_EN)</t>
+          <t>DRB102 83 = c83 'EHPS enable +12 V'; channels.csv mrs_eps c1 Enable (MRS_EN)</t>
         </is>
       </c>
       <c r="AF4" s="54" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="AG4" s="54" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_hv_mrs_en_e_ae on A-engine, 240 mm; w_hv_mrs_en_e on EngineRoom-C, 1460 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_hv_mrs_en_e_ae on ECU-engine, 240 mm; w_hv_mrs_en_e on EngineRoom-C, 1460 mm)</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="D5" s="23" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="E5" s="24" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>bh_a_eng</t>
+          <t>bh_eng</t>
         </is>
       </c>
       <c r="G5" s="26" t="inlineStr">
@@ -1468,7 +1468,7 @@
       <c r="AD5" s="38" t="inlineStr"/>
       <c r="AE5" s="38" t="inlineStr">
         <is>
-          <t>DRB102 84 = loom A c84 'ECU-A A27'; channels.csv mrs_eps b2 SPD (AUX7_MRS_SPD)</t>
+          <t>DRB102 84 = c84 'ECU-A A27'; channels.csv mrs_eps b2 SPD (AUX7_MRS_SPD)</t>
         </is>
       </c>
       <c r="AF5" s="38" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AG5" s="38" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_mrs_e_ae on A-engine, 240 mm; w_mrs_e on EngineRoom-C, 1460 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_mrs_e_ae on ECU-engine, 240 mm; w_mrs_e on EngineRoom-C, 1460 mm)</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>A-engine</t>
+          <t>ECU-engine</t>
         </is>
       </c>
       <c r="E6" s="40" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>bh_a_eng</t>
+          <t>bh_eng</t>
         </is>
       </c>
       <c r="G6" s="42" t="inlineStr">
@@ -1589,7 +1589,7 @@
       <c r="AD6" s="54" t="inlineStr"/>
       <c r="AE6" s="54" t="inlineStr">
         <is>
-          <t>DRB102 85 = loom A c85 'EHPS relay coil (-)'; channels.csv mrs_eps b5 Relay (MRS_RLY)</t>
+          <t>DRB102 85 = c85 'EHPS relay coil (-)'; channels.csv mrs_eps b5 Relay (MRS_RLY)</t>
         </is>
       </c>
       <c r="AF6" s="54" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AG6" s="54" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_eps_rly_ae on A-engine, 240 mm; w_eps_rly_e on EngineRoom-C, 1460 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_eps_rly_ae on ECU-engine, 240 mm; w_eps_rly_e on EngineRoom-C, 1460 mm)</t>
         </is>
       </c>
     </row>
